--- a/Тест2/278.xlsx
+++ b/Тест2/278.xlsx
@@ -105,19 +105,19 @@
     <t xml:space="preserve">Dastlabki zenginlashtirishning vazifasi nima?</t>
   </si>
   <si>
-    <t xml:space="preserve">Salmonellalarni darhol o'ldirib yuborish</t>
+    <t xml:space="preserve">Salmonellalarni darhol o'ldirib yuborish uchun</t>
   </si>
   <si>
     <t xml:space="preserve">Jarohatlangan hujayralarni tiklash va ko'paytirish</t>
   </si>
   <si>
-    <t xml:space="preserve">Namunani qizdirib sterillab qo'yish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boshqa mikroblarni butunlay ko'paytirish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Namuna rangini o'zgartirib qo'yish</t>
+    <t xml:space="preserve">Namunani qizdirib sterillab qo'yish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boshqa mikroblarni butunlay ko'paytirish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Namuna rangini o'zgartirib qo'yish uchun</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Jarohatlangan hujayralarni tiklash va ko'paytirish. Dastlabki zenginlashtirishda salmonellalar boshqa mikroblardan oldin ko'payadi va jarohatlangan hujayralar tiklanadi. Manba: Mavzu materiali (278.docx).</t>
